--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260608.xlsx
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>28,999,000</t>
+          <t>11,458,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,458,000</t>
+          <t>28,999,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
